--- a/Excel/PANEL-GLIDE.xlsx
+++ b/Excel/PANEL-GLIDE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\BOOS\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9905CF2D-93E4-40F9-AE52-C64DF98C63AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC3FBA9-71E4-4832-B806-A3BB75FFDC99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23880" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{391A9620-3F13-4AFF-B5D6-F90AA0405B29}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>BLIND TYPE</t>
   </si>
@@ -64,9 +64,6 @@
     <t>SLIDING DOOR</t>
   </si>
   <si>
-    <t>Face Fit</t>
-  </si>
-  <si>
     <t>White</t>
   </si>
   <si>
@@ -101,6 +98,21 @@
   </si>
   <si>
     <t>Coffee</t>
+  </si>
+  <si>
+    <t>Your Order Number</t>
+  </si>
+  <si>
+    <t>Your Order Name</t>
+  </si>
+  <si>
+    <t>Your Order Note</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Opening Size Face Fit</t>
   </si>
 </sst>
 </file>
@@ -243,7 +255,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,6 +433,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -584,8 +602,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -941,15 +960,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49A31EDF-8B5E-4C74-8FF3-398CC77AAB69}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.85546875" customWidth="1"/>
     <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.5703125" customWidth="1"/>
@@ -962,149 +981,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" t="s">
-        <v>23</v>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
+      <c r="H3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3">
+      <c r="I3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3">
+      <c r="J3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3">
+      <c r="K3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H3">
+      <c r="L3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I3">
+      <c r="M3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J3">
+      <c r="N3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="K3">
-        <v>11</v>
-      </c>
-      <c r="L3">
-        <v>12</v>
-      </c>
-      <c r="M3">
-        <v>13</v>
-      </c>
-      <c r="N3">
-        <v>14</v>
-      </c>
-      <c r="O3">
-        <v>15</v>
-      </c>
-      <c r="P3">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4">
+        <v>1000</v>
+      </c>
+      <c r="K4">
+        <v>1000</v>
+      </c>
+      <c r="M4">
         <v>2</v>
       </c>
-      <c r="H4" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L4" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" t="s">
-        <v>9</v>
-      </c>
       <c r="N4" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4" t="s">
-        <v>20</v>
-      </c>
-      <c r="P4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5">
-        <v>1000</v>
-      </c>
-      <c r="K5">
-        <v>1000</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/PANEL-GLIDE.xlsx
+++ b/Excel/PANEL-GLIDE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\BOOS\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC3FBA9-71E4-4832-B806-A3BB75FFDC99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B033DA-0819-4617-9F24-FF9D63196C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23880" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{391A9620-3F13-4AFF-B5D6-F90AA0405B29}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="35">
   <si>
     <t>BLIND TYPE</t>
   </si>
@@ -113,6 +113,18 @@
   </si>
   <si>
     <t>Opening Size Face Fit</t>
+  </si>
+  <si>
+    <t>Plantation</t>
+  </si>
+  <si>
+    <t>Panel Only</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Track Only</t>
   </si>
 </sst>
 </file>
@@ -960,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49A31EDF-8B5E-4C74-8FF3-398CC77AAB69}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
@@ -1093,6 +1105,141 @@
         <v>29</v>
       </c>
     </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5">
+        <v>1000</v>
+      </c>
+      <c r="K5">
+        <v>1000</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6">
+        <v>1000</v>
+      </c>
+      <c r="K6">
+        <v>1000</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7">
+        <v>1000</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
+        <v>1000</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
